--- a/File mẫu excel/Danh_sach_diem_hoc_phan_Co_so_tu_nhien_va_xa_hoi.xlsx
+++ b/File mẫu excel/Danh_sach_diem_hoc_phan_Co_so_tu_nhien_va_xa_hoi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HỆ THỐNG QUẢN LÍ SINH VIÊN PHHG\unihubhg\File mẫu excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE97C80C-DAFC-44C8-BA42-BAB463A87739}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE91E4FB-4C98-4490-A336-A829DC0AD386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
